--- a/KatalonData/RADTestData/BeforePayments.xlsx
+++ b/KatalonData/RADTestData/BeforePayments.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B34142-0BD7-480B-8464-85977A0636C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{D3B34142-0BD7-480B-8464-85977A0636C2}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-2010" windowWidth="28995" windowHeight="15675" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView activeTab="3" windowHeight="15675" windowWidth="28995" xWindow="14303" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-2010"/>
   </bookViews>
   <sheets>
-    <sheet name="Estimated" sheetId="1" r:id="rId1"/>
-    <sheet name="Existing" sheetId="2" r:id="rId2"/>
-    <sheet name="Extension" sheetId="3" r:id="rId3"/>
-    <sheet name="NewTaxReturn" sheetId="4" r:id="rId4"/>
-    <sheet name="Personal" sheetId="5" r:id="rId5"/>
-    <sheet name="Personal_IND" sheetId="6" r:id="rId6"/>
-    <sheet name="Personal_JNT" sheetId="7" r:id="rId7"/>
-    <sheet name="Personal_EL" sheetId="8" r:id="rId8"/>
+    <sheet name="Estimated" r:id="rId1" sheetId="1"/>
+    <sheet name="Existing" r:id="rId2" sheetId="2"/>
+    <sheet name="Extension" r:id="rId3" sheetId="3"/>
+    <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
+    <sheet name="Personal" r:id="rId5" sheetId="5"/>
+    <sheet name="Personal_IND" r:id="rId6" sheetId="6"/>
+    <sheet name="Personal_JNT" r:id="rId7" sheetId="7"/>
+    <sheet name="Personal_EL" r:id="rId8" sheetId="8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$61</definedName>
+    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">NewTaxReturn!$E$1:$E$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="228">
   <si>
     <t>Result</t>
   </si>
@@ -724,12 +724,19 @@
   </si>
   <si>
     <t>This is in QA and Demo but not in Production</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thu Nov 27 16:52:17 EST 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -778,19 +785,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -807,10 +814,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -845,7 +852,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -897,7 +904,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1008,21 +1015,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1039,7 +1046,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1091,28 +1098,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:J7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.1796875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.54296875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.54296875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.26953125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.54296875" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.1796875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.453125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1149,10 +1156,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1335,8 +1342,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1344,20 +1351,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
-  <dimension ref="A1:J21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.6328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.1796875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.1796875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.36328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.26953125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.6328125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.453125" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.1796875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.36328125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1856,7 +1863,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1864,19 +1871,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
-  <dimension ref="A1:I7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.26953125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.1796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.453125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2063,7 +2070,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2071,20 +2078,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:L61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1796875" style="1" collapsed="1"/>
-    <col min="12" max="12" width="43.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.7265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.26953125" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.81640625" collapsed="true"/>
+    <col min="11" max="11" style="1" width="9.1796875" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="43.1796875" collapsed="true"/>
+    <col min="13" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -3769,7 +3776,7 @@
   </sheetData>
   <autoFilter ref="E1:E61" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3777,16 +3784,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="26.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.453125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="26.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -3891,7 +3898,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3899,18 +3906,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
-  <dimension ref="A1:H9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.1796875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.1796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.453125" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -4115,23 +4122,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
-  <dimension ref="A1:G6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.453125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.1796875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -4273,21 +4280,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.453125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.7265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -4348,6 +4355,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/BeforePayments.xlsx
+++ b/KatalonData/RADTestData/BeforePayments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{D3B34142-0BD7-480B-8464-85977A0636C2}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{A55B5BD7-60D1-4D2D-89E1-6A1B1ADDA73D}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="3" windowHeight="15675" windowWidth="28995" xWindow="14303" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-2010"/>
+    <workbookView activeTab="3" windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-98"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" r:id="rId1" sheetId="1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="330">
   <si>
     <t>Result</t>
   </si>
@@ -423,313 +423,619 @@
     <t>Incorrect App ID</t>
   </si>
   <si>
-    <t>Mon Oct 13 20:52:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:53:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:54:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:54:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:55:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:56:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:56:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:57:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:58:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 20:58:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:00:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:00:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:01:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:13:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:14:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:15:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:15:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:16:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:17:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:18:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:19:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:20:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:21:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:21:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:22:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:24:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:24:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:25:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:26:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:27:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:28:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:28:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:33:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:34:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:35:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:37:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:38:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:38:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:40:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:41:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:42:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:42:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:43:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:44:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:45:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:46:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:46:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:47:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:49:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:50:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:51:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:52:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:52:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 13 21:58:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 14:57:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 14:58:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 14:58:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 14:59:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 15:00:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 15:03:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 15:03:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 15:04:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 15:05:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 15:06:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:16:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:17:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:18:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:19:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:19:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:20:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:26:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:27:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 22:29:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 15:50:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 15:57:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 15:58:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 16:25:09 EST 2025</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Wed Nov 05 16:47:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 16:48:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 16:49:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 16:49:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 16:50:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 16:51:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 17:02:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 17:07:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 17:49:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 17:50:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 18:09:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 18:18:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:13:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:14:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:15:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:16:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:17:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:18:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:33:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:51:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 20:57:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 21:04:23 EST 2025</t>
-  </si>
-  <si>
     <t>This is in QA and Demo but not in Production</t>
   </si>
   <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:27:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:28:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:28:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:29:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:30:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:31:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:31:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:32:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:33:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:34:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:34:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:35:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:36:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:37:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:38:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:38:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:39:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:40:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:41:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:41:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:42:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:43:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:44:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:44:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:45:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:46:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:47:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:47:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:48:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:49:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:50:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:50:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:51:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:52:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:53:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:53:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:54:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:55:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:55:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:56:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:57:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:58:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:58:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 23:59:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:00:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:01:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:01:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:02:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:03:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:04:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:04:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:05:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:06:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:07:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:07:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:08:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:09:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:09:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:10:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:11:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:12:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:12:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:13:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:14:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:15:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:16:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:16:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:17:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:18:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:18:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:19:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:20:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:21:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:21:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:22:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:23:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:24:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:24:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:25:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:26:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:26:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:27:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:28:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:29:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:29:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:30:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:31:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:32:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:33:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:34:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:35:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:35:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:36:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:37:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:38:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:38:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:39:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:40:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:41:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 00:42:21 EDT 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Thu Nov 27 16:52:17 EST 2025</t>
+    <t>Fri May 29 11:16:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:05:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:06:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:07:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:08:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:09:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:10:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:11:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:12:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:13:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:15:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:16:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:17:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:18:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:19:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:20:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:21:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:22:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:24:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:25:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:26:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:27:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:28:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:29:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:31:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:32:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:33:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:35:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:36:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:37:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:38:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:40:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:41:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:42:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:43:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:44:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:45:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:46:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:48:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:49:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:50:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:51:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:52:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:53:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:54:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:56:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:57:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:58:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 19:59:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:00:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:01:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:02:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:04:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:05:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:06:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:07:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:08:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:09:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:10:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:12:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:13:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:14:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:15:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:16:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:17:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:18:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:20:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:21:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:22:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:23:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:24:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:25:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:26:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:28:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:29:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:30:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:31:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:32:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:33:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:34:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:36:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:37:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:38:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:39:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:40:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:42:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:43:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:45:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:47:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:48:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:50:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:51:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:52:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:53:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:55:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:56:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:57:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:58:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 20:59:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:00:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:02:11 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1106,23 +1412,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.1796875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.54296875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.54296875" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.26953125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.54296875" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.1796875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.453125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1154,12 +1460,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1171,7 +1477,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -1183,12 +1489,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1200,7 +1506,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -1212,12 +1518,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1229,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1244,12 +1550,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1261,7 +1567,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1276,12 +1582,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>234</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1293,7 +1599,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1308,12 +1614,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1325,7 +1631,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
@@ -1338,6 +1644,29 @@
       </c>
       <c r="J7" s="1" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1353,21 +1682,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.26953125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.6328125" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
     <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.453125" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.1796875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.36328125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1399,12 +1728,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>237</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1422,12 +1751,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>238</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1445,12 +1774,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>239</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1468,12 +1797,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1494,12 +1823,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1520,12 +1849,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1543,12 +1872,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1566,12 +1895,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1589,12 +1918,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1612,12 +1941,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>246</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1635,12 +1964,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1658,12 +1987,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1681,12 +2010,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1704,12 +2033,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1724,12 +2053,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1750,12 +2079,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1773,12 +2102,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1796,7 +2125,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1819,15 +2148,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>111</v>
@@ -1836,18 +2165,18 @@
         <v>115</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>111</v>
@@ -1859,7 +2188,7 @@
         <v>32</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>225</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1873,20 +2202,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.26953125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.453125" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
     <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1915,12 +2244,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1932,7 +2261,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -1941,12 +2270,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1958,18 +2287,18 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1981,7 +2310,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>32</v>
@@ -1990,12 +2319,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2007,7 +2336,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>32</v>
@@ -2016,12 +2345,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2033,7 +2362,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>32</v>
@@ -2042,12 +2371,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2059,7 +2388,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>32</v>
@@ -2080,21 +2409,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
   <dimension ref="A1:M61"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.1796875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.7265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.26953125" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.81640625" collapsed="true"/>
-    <col min="11" max="11" style="1" width="9.1796875" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="43.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" style="1" width="9.19921875" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="13" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2132,12 +2461,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2148,19 +2477,19 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1">
-        <v>2024</v>
+      <c r="F2" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2171,8 +2500,8 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1">
-        <v>2024</v>
+      <c r="F3" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>32</v>
@@ -2181,12 +2510,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2197,8 +2526,8 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1">
-        <v>2024</v>
+      <c r="F4" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>32</v>
@@ -2207,12 +2536,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2223,8 +2552,8 @@
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1">
-        <v>2024</v>
+      <c r="F5" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>32</v>
@@ -2233,12 +2562,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2249,8 +2578,8 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1">
-        <v>2024</v>
+      <c r="F6" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>32</v>
@@ -2259,12 +2588,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>267</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2275,19 +2604,19 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1">
-        <v>2023</v>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2298,8 +2627,8 @@
       <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
-        <v>2023</v>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
@@ -2308,12 +2637,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>269</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2324,8 +2653,8 @@
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="1">
-        <v>2023</v>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>32</v>
@@ -2334,12 +2663,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2350,8 +2679,8 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1">
-        <v>2023</v>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>32</v>
@@ -2360,12 +2689,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2376,8 +2705,8 @@
       <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="1">
-        <v>2023</v>
+      <c r="F11" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>32</v>
@@ -2386,12 +2715,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2402,19 +2731,19 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1">
-        <v>2022</v>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>273</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2425,8 +2754,8 @@
       <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1">
-        <v>2022</v>
+      <c r="F13" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>32</v>
@@ -2435,12 +2764,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>274</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2451,8 +2780,8 @@
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="1">
-        <v>2022</v>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
@@ -2461,12 +2790,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>275</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2477,8 +2806,8 @@
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="1">
-        <v>2022</v>
+      <c r="F15" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
@@ -2487,12 +2816,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>276</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2503,8 +2832,8 @@
       <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1">
-        <v>2022</v>
+      <c r="F16" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>32</v>
@@ -2513,12 +2842,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2529,8 +2858,8 @@
       <c r="E17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="1">
-        <v>2025</v>
+      <c r="F17" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -2542,12 +2871,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>278</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2558,8 +2887,8 @@
       <c r="E18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="1">
-        <v>2025</v>
+      <c r="F18" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
@@ -2571,12 +2900,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>279</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2587,8 +2916,8 @@
       <c r="E19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="1">
-        <v>2025</v>
+      <c r="F19" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -2600,12 +2929,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>280</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2616,19 +2945,19 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1">
-        <v>2024</v>
+      <c r="F20" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>281</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2639,8 +2968,8 @@
       <c r="E21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="1">
-        <v>2025</v>
+      <c r="F21" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>98</v>
@@ -2652,12 +2981,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>282</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2668,8 +2997,8 @@
       <c r="E22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="1">
-        <v>2025</v>
+      <c r="F22" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
@@ -2681,12 +3010,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>283</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2697,8 +3026,8 @@
       <c r="E23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="1">
-        <v>2025</v>
+      <c r="F23" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>32</v>
@@ -2707,12 +3036,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>284</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2723,8 +3052,8 @@
       <c r="E24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="1">
-        <v>2025</v>
+      <c r="F24" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
@@ -2736,12 +3065,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2752,8 +3081,8 @@
       <c r="E25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="1">
-        <v>2025</v>
+      <c r="F25" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2768,12 +3097,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2784,8 +3113,8 @@
       <c r="E26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="1">
-        <v>2025</v>
+      <c r="F26" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
@@ -2797,12 +3126,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>287</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2813,8 +3142,8 @@
       <c r="E27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="1">
-        <v>2025</v>
+      <c r="F27" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
@@ -2826,12 +3155,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>197</v>
+        <v>288</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2842,8 +3171,8 @@
       <c r="E28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="1">
-        <v>2025</v>
+      <c r="F28" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
@@ -2858,12 +3187,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>289</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2874,8 +3203,8 @@
       <c r="E29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="1">
-        <v>2024</v>
+      <c r="F29" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>32</v>
@@ -2887,12 +3216,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2904,7 +3233,7 @@
         <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>32</v>
@@ -2916,12 +3245,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>159</v>
+        <v>291</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2932,8 +3261,8 @@
       <c r="E31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="1">
-        <v>2024</v>
+      <c r="F31" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>32</v>
@@ -2945,12 +3274,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>213</v>
+        <v>292</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2961,19 +3290,19 @@
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="1">
-        <v>2023</v>
+      <c r="F32" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>293</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2984,8 +3313,8 @@
       <c r="E33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="1">
-        <v>2024</v>
+      <c r="F33" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>98</v>
@@ -2997,12 +3326,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>294</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -3013,8 +3342,8 @@
       <c r="E34" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F34" s="1">
-        <v>2024</v>
+      <c r="F34" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>32</v>
@@ -3026,12 +3355,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -3042,8 +3371,8 @@
       <c r="E35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="1">
-        <v>2024</v>
+      <c r="F35" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>32</v>
@@ -3052,12 +3381,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -3068,8 +3397,8 @@
       <c r="E36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="1">
-        <v>2024</v>
+      <c r="F36" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>32</v>
@@ -3081,12 +3410,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
+        <v>297</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -3097,8 +3426,8 @@
       <c r="E37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="1">
-        <v>2024</v>
+      <c r="F37" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>32</v>
@@ -3113,12 +3442,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>298</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -3129,8 +3458,8 @@
       <c r="E38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="1">
-        <v>2024</v>
+      <c r="F38" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>32</v>
@@ -3142,12 +3471,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3158,8 +3487,8 @@
       <c r="E39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="1">
-        <v>2024</v>
+      <c r="F39" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>32</v>
@@ -3171,12 +3500,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>300</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3187,8 +3516,8 @@
       <c r="E40" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="1">
-        <v>2024</v>
+      <c r="F40" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>32</v>
@@ -3203,12 +3532,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>301</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3219,8 +3548,8 @@
       <c r="E41" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="1">
-        <v>2023</v>
+      <c r="F41" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>32</v>
@@ -3232,12 +3561,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>168</v>
+        <v>302</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3248,8 +3577,8 @@
       <c r="E42" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F42" s="1">
-        <v>2023</v>
+      <c r="F42" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>32</v>
@@ -3261,12 +3590,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>169</v>
+        <v>303</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3277,8 +3606,8 @@
       <c r="E43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="1">
-        <v>2023</v>
+      <c r="F43" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>32</v>
@@ -3290,12 +3619,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>304</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3306,19 +3635,19 @@
       <c r="E44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="1">
-        <v>2022</v>
+      <c r="F44" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>35</v>
       </c>
       <c r="B45" t="s">
-        <v>171</v>
+        <v>305</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3329,8 +3658,8 @@
       <c r="E45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="1">
-        <v>2023</v>
+      <c r="F45" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>98</v>
@@ -3342,12 +3671,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>306</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3358,8 +3687,8 @@
       <c r="E46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="1">
-        <v>2023</v>
+      <c r="F46" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>32</v>
@@ -3371,12 +3700,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>214</v>
+        <v>307</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3387,8 +3716,8 @@
       <c r="E47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="1">
-        <v>2023</v>
+      <c r="F47" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>32</v>
@@ -3397,12 +3726,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>308</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3413,8 +3742,8 @@
       <c r="E48" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F48" s="1">
-        <v>2023</v>
+      <c r="F48" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>32</v>
@@ -3426,12 +3755,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3442,8 +3771,8 @@
       <c r="E49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="1">
-        <v>2023</v>
+      <c r="F49" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>32</v>
@@ -3458,12 +3787,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>175</v>
+        <v>310</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3474,8 +3803,8 @@
       <c r="E50" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F50" s="1">
-        <v>2023</v>
+      <c r="F50" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>32</v>
@@ -3487,12 +3816,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>311</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3503,8 +3832,8 @@
       <c r="E51" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F51" s="1">
-        <v>2023</v>
+      <c r="F51" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>32</v>
@@ -3516,12 +3845,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>35</v>
       </c>
       <c r="B52" t="s">
-        <v>177</v>
+        <v>312</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3532,8 +3861,8 @@
       <c r="E52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="1">
-        <v>2023</v>
+      <c r="F52" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>32</v>
@@ -3548,15 +3877,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>313</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>16</v>
@@ -3565,21 +3894,21 @@
         <v>115</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3588,16 +3917,16 @@
         <v>114</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -3614,7 +3943,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
@@ -3623,15 +3952,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>315</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>16</v>
@@ -3640,21 +3969,21 @@
         <v>115</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>218</v>
+        <v>316</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3663,16 +3992,16 @@
         <v>114</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>35</v>
       </c>
@@ -3689,7 +4018,7 @@
         <v>45</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>32</v>
@@ -3698,15 +4027,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>16</v>
@@ -3715,21 +4044,21 @@
         <v>115</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B60" t="s">
-        <v>220</v>
+        <v>318</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -3738,16 +4067,16 @@
         <v>114</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>35</v>
       </c>
@@ -3764,7 +4093,7 @@
         <v>45</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>32</v>
@@ -3786,17 +4115,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="26.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="26.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3816,7 +4145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C2" s="1" t="s">
         <v>32</v>
       </c>
@@ -3830,7 +4159,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3841,7 +4170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
         <v>36</v>
       </c>
@@ -3855,7 +4184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
@@ -3869,7 +4198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
@@ -3883,7 +4212,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
@@ -3908,19 +4237,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.453125" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3946,12 +4275,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>320</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3963,18 +4292,18 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>321</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3986,18 +4315,18 @@
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>322</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4009,18 +4338,18 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4032,18 +4361,18 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>324</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4055,13 +4384,13 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -4081,7 +4410,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -4101,7 +4430,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -4129,19 +4458,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.1796875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4164,12 +4493,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4181,18 +4510,18 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>326</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4204,18 +4533,18 @@
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>327</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4227,18 +4556,18 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4250,18 +4579,18 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>329</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4273,7 +4602,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>94</v>
@@ -4287,17 +4616,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.7265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4317,12 +4646,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4337,7 +4666,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>

--- a/KatalonData/RADTestData/BeforePayments.xlsx
+++ b/KatalonData/RADTestData/BeforePayments.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{A55B5BD7-60D1-4D2D-89E1-6A1B1ADDA73D}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70909A88-31CC-4438-BD2B-0DEBB3DD01B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="3" windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-98"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Estimated" r:id="rId1" sheetId="1"/>
-    <sheet name="Existing" r:id="rId2" sheetId="2"/>
-    <sheet name="Extension" r:id="rId3" sheetId="3"/>
-    <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
-    <sheet name="Personal" r:id="rId5" sheetId="5"/>
-    <sheet name="Personal_IND" r:id="rId6" sheetId="6"/>
-    <sheet name="Personal_JNT" r:id="rId7" sheetId="7"/>
-    <sheet name="Personal_EL" r:id="rId8" sheetId="8"/>
+    <sheet name="Estimated" sheetId="1" r:id="rId1"/>
+    <sheet name="Existing" sheetId="2" r:id="rId2"/>
+    <sheet name="Extension" sheetId="3" r:id="rId3"/>
+    <sheet name="NewTaxReturn" sheetId="4" r:id="rId4"/>
+    <sheet name="Personal" sheetId="5" r:id="rId5"/>
+    <sheet name="Personal_IND" sheetId="6" r:id="rId6"/>
+    <sheet name="Personal_JNT" sheetId="7" r:id="rId7"/>
+    <sheet name="Personal_EL" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">NewTaxReturn!$E$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="228">
   <si>
     <t>Result</t>
   </si>
@@ -432,312 +432,6 @@
     <t>2026</t>
   </si>
   <si>
-    <t>Thu May 28 23:27:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:28:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:28:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:29:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:30:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:31:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:31:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:32:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:33:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:34:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:34:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:35:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:36:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:37:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:38:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:38:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:39:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:40:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:41:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:41:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:42:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:43:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:44:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:44:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:45:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:46:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:47:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:47:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:48:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:49:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:50:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:50:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:51:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:52:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:53:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:53:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:54:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:55:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:55:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:56:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:57:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:58:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:58:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 28 23:59:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:00:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:01:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:01:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:02:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:03:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:04:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:04:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:05:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:06:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:07:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:07:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:08:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:09:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:09:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:10:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:11:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:12:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:12:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:13:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:14:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:15:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:16:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:16:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:17:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:18:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:18:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:19:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:20:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:21:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:21:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:22:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:23:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:24:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:24:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:25:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:26:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:26:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:27:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:28:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:29:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:29:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:30:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:31:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:32:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:33:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:34:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:35:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:35:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:36:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:37:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:38:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:38:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:39:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:40:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:41:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 00:42:21 EDT 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Fri May 29 11:16:53 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri May 29 19:05:10 EDT 2026</t>
   </si>
   <si>
@@ -756,9 +450,6 @@
     <t>Fri May 29 19:10:17 EDT 2026</t>
   </si>
   <si>
-    <t>Fri May 29 19:11:18 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri May 29 19:12:46 EDT 2026</t>
   </si>
   <si>
@@ -1036,13 +727,15 @@
   </si>
   <si>
     <t>Fri May 29 21:02:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 16:56:28 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1091,19 +784,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1120,10 +813,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1158,7 +851,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1210,7 +903,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1321,21 +1014,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1352,7 +1045,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1404,28 +1097,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:K8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1465,7 +1158,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1494,7 +1187,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>129</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1523,7 +1216,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>130</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1555,7 +1248,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1587,7 +1280,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1619,7 +1312,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>133</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1651,7 +1344,7 @@
         <v>125</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1671,8 +1364,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1680,20 +1373,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1733,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1756,7 +1449,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1779,7 +1472,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>136</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1802,7 +1495,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1828,7 +1521,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1854,7 +1547,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1877,7 +1570,7 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1900,7 +1593,7 @@
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1923,7 +1616,7 @@
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1946,7 +1639,7 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1969,7 +1662,7 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1992,7 +1685,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>145</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2015,7 +1708,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2038,7 +1731,7 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>147</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2058,7 +1751,7 @@
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2084,7 +1777,7 @@
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2107,7 +1800,7 @@
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2153,7 +1846,7 @@
         <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2173,7 +1866,7 @@
         <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2192,7 +1885,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2200,19 +1893,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
-  <dimension ref="A1:J7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2249,7 +1942,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2275,7 +1968,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2298,7 +1991,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2324,7 +2017,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2350,7 +2043,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2376,7 +2069,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2399,7 +2092,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2407,20 +2100,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:M61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="11" max="11" style="1" width="9.19921875" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
-    <col min="13" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
+    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
@@ -2466,7 +2159,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2489,7 +2182,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2515,7 +2208,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>161</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2541,7 +2234,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>162</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2567,7 +2260,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>163</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2593,7 +2286,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>164</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2616,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>165</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2642,7 +2335,7 @@
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>166</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2668,7 +2361,7 @@
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2694,7 +2387,7 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>168</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2720,7 +2413,7 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>169</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2743,7 +2436,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>170</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2769,7 +2462,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2795,7 +2488,7 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2821,7 +2514,7 @@
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>173</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2847,7 +2540,7 @@
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>174</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2876,7 +2569,7 @@
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>175</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2905,7 +2598,7 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>176</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2934,7 +2627,7 @@
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>177</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2957,7 +2650,7 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2986,7 +2679,7 @@
         <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>179</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -3015,7 +2708,7 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>283</v>
+        <v>180</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -3041,7 +2734,7 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -3070,7 +2763,7 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -3102,7 +2795,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>286</v>
+        <v>183</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -3131,7 +2824,7 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>287</v>
+        <v>184</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -3160,7 +2853,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -3192,7 +2885,7 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>289</v>
+        <v>186</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -3221,7 +2914,7 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>290</v>
+        <v>187</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -3250,7 +2943,7 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>291</v>
+        <v>188</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -3279,7 +2972,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -3302,7 +2995,7 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>293</v>
+        <v>190</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -3331,7 +3024,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>294</v>
+        <v>191</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -3360,7 +3053,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -3386,7 +3079,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>296</v>
+        <v>193</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -3415,7 +3108,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>297</v>
+        <v>194</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -3447,7 +3140,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>298</v>
+        <v>195</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -3476,7 +3169,7 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>299</v>
+        <v>196</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3505,7 +3198,7 @@
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>300</v>
+        <v>197</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3537,7 +3230,7 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>301</v>
+        <v>198</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3566,7 +3259,7 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>302</v>
+        <v>199</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3595,7 +3288,7 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>303</v>
+        <v>200</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3624,7 +3317,7 @@
         <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>304</v>
+        <v>201</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3647,7 +3340,7 @@
         <v>35</v>
       </c>
       <c r="B45" t="s">
-        <v>305</v>
+        <v>202</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3676,7 +3369,7 @@
         <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>306</v>
+        <v>203</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3705,7 +3398,7 @@
         <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>307</v>
+        <v>204</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3731,7 +3424,7 @@
         <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>308</v>
+        <v>205</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3760,7 +3453,7 @@
         <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>309</v>
+        <v>206</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3792,7 +3485,7 @@
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>310</v>
+        <v>207</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3821,7 +3514,7 @@
         <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>311</v>
+        <v>208</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3850,7 +3543,7 @@
         <v>35</v>
       </c>
       <c r="B52" t="s">
-        <v>312</v>
+        <v>209</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3882,7 +3575,7 @@
         <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>313</v>
+        <v>210</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3905,7 +3598,7 @@
         <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>314</v>
+        <v>211</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -3957,7 +3650,7 @@
         <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>315</v>
+        <v>212</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3980,7 +3673,7 @@
         <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>316</v>
+        <v>213</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -4032,7 +3725,7 @@
         <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>317</v>
+        <v>214</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -4055,7 +3748,7 @@
         <v>125</v>
       </c>
       <c r="B60" t="s">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -4105,7 +3798,7 @@
   </sheetData>
   <autoFilter ref="E1:E61" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -4113,16 +3806,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="26.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="26.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4227,7 +3920,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -4235,18 +3928,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
-  <dimension ref="A1:I9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -4280,7 +3973,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>217</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4303,7 +3996,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4326,7 +4019,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>219</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4349,7 +4042,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>220</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4372,7 +4065,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>221</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4451,23 +4144,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
-  <dimension ref="A1:H6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4498,7 +4191,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>222</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4521,7 +4214,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>223</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4544,7 +4237,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4567,7 +4260,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>225</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4590,7 +4283,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>226</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4609,21 +4302,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4651,7 +4344,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>216</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4684,6 +4377,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/BeforePayments.xlsx
+++ b/KatalonData/RADTestData/BeforePayments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70909A88-31CC-4438-BD2B-0DEBB3DD01B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5865EEBB-5A1B-47FE-8F5F-EAC23505C708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="324">
   <si>
     <t>Result</t>
   </si>
@@ -396,18 +396,6 @@
     <t>Digital Advertising Gross Revenues</t>
   </si>
   <si>
-    <t>Mon Feb 17 18:36:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 17 19:31:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 17 19:34:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 17 19:36:46 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 17 19:38:28 EST 2025</t>
   </si>
   <si>
@@ -504,9 +492,6 @@
     <t>Fri May 29 19:32:12 EDT 2026</t>
   </si>
   <si>
-    <t>Fri May 29 19:33:50 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri May 29 19:35:27 EDT 2026</t>
   </si>
   <si>
@@ -654,9 +639,6 @@
     <t>Fri May 29 20:30:25 EDT 2026</t>
   </si>
   <si>
-    <t>Fri May 29 20:31:34 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri May 29 20:32:43 EDT 2026</t>
   </si>
   <si>
@@ -681,21 +663,9 @@
     <t>Fri May 29 20:40:44 EDT 2026</t>
   </si>
   <si>
-    <t>Fri May 29 20:42:20 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri May 29 20:43:57 EDT 2026</t>
   </si>
   <si>
-    <t>Fri May 29 20:45:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:47:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:48:54 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri May 29 20:50:31 EDT 2026</t>
   </si>
   <si>
@@ -730,12 +700,331 @@
   </si>
   <si>
     <t>Tue Jun 02 16:56:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>MFInsNum</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:27:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:27:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:28:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:29:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:30:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:23:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:24:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:24:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:25:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:25:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:26:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:27:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:27:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:28:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:29:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:30:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:30:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:31:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:32:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:32:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:33:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:34:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:35:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:35:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:36:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:37:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:38:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:38:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:39:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:40:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:41:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:41:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:42:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:43:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:43:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:44:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:45:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:46:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:46:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:47:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:47:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:48:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:49:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:49:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:50:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:51:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:51:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:52:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:53:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:53:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:54:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:54:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:55:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:56:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:56:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:57:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:58:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:58:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:59:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:00:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:00:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:01:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:02:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:02:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:03:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:04:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:04:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:05:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:05:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:06:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:07:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:07:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:08:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:09:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:10:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:10:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:11:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:11:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:12:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:13:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:13:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:14:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:15:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:15:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:16:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:17:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:17:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:18:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:19:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:19:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:20:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:21:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:21:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:22:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:23:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:23:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:24:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:25:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:26:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:26:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:27:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:28:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:29:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:30:02 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1108,17 +1397,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1154,11 +1443,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>128</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1170,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -1183,11 +1472,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1199,7 +1488,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -1212,11 +1501,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>130</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1228,7 +1517,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1244,11 +1533,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>131</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1260,7 +1549,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1276,11 +1565,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>132</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1292,7 +1581,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1308,11 +1597,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>133</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1324,7 +1613,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
@@ -1340,11 +1629,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" t="s">
-        <v>227</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1356,7 +1645,7 @@
         <v>115</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>102</v>
@@ -1377,16 +1666,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1422,11 +1711,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>134</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1445,11 +1734,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>135</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1468,11 +1757,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>136</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1491,11 +1780,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>137</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1517,11 +1806,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>138</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1543,11 +1832,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>139</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1566,11 +1855,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>140</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1589,11 +1878,11 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>141</v>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1612,11 +1901,11 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>142</v>
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1635,11 +1924,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>143</v>
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1658,11 +1947,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>144</v>
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1681,11 +1970,11 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>145</v>
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1704,11 +1993,11 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>146</v>
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1727,11 +2016,11 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>147</v>
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1747,11 +2036,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>148</v>
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1773,11 +2062,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>149</v>
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1796,11 +2085,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>150</v>
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1819,12 +2108,6 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>116</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1842,11 +2125,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" t="s">
-        <v>151</v>
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1858,18 +2141,12 @@
         <v>115</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" t="s">
-        <v>152</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>111</v>
@@ -1881,7 +2158,7 @@
         <v>32</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1897,15 +2174,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1938,11 +2215,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>153</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1964,11 +2241,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>154</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1987,11 +2264,11 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>155</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2013,11 +2290,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>156</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2039,11 +2316,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>157</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2065,11 +2342,11 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>158</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2101,22 +2378,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
-    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2148,18 +2426,21 @@
         <v>112</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>159</v>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2173,16 +2454,16 @@
       <c r="F2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>160</v>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2199,16 +2480,16 @@
       <c r="G3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>161</v>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2225,16 +2506,16 @@
       <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>162</v>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2251,16 +2532,16 @@
       <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>163</v>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2277,16 +2558,16 @@
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>164</v>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2300,16 +2581,16 @@
       <c r="F7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>165</v>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2326,16 +2607,16 @@
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>166</v>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2352,16 +2633,16 @@
       <c r="G9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>167</v>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2378,16 +2659,16 @@
       <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>168</v>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2404,16 +2685,16 @@
       <c r="G11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>169</v>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2427,16 +2708,16 @@
       <c r="F12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>170</v>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2453,16 +2734,16 @@
       <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>171</v>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2479,16 +2760,16 @@
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>172</v>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2505,16 +2786,16 @@
       <c r="G15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>173</v>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2531,16 +2812,16 @@
       <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>174</v>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2552,7 +2833,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -2560,16 +2841,16 @@
       <c r="I17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>175</v>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2581,7 +2862,7 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
@@ -2589,16 +2870,16 @@
       <c r="I18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>176</v>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2610,7 +2891,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -2618,16 +2899,16 @@
       <c r="I19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>177</v>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2641,16 +2922,16 @@
       <c r="F20" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>178</v>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2662,7 +2943,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>98</v>
@@ -2670,16 +2951,16 @@
       <c r="J21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>179</v>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2691,7 +2972,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
@@ -2699,16 +2980,16 @@
       <c r="I22" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
-        <v>180</v>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2720,21 +3001,21 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>181</v>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2746,7 +3027,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
@@ -2754,16 +3035,16 @@
       <c r="I24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>182</v>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2775,7 +3056,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2786,16 +3067,16 @@
       <c r="I25" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>183</v>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2807,7 +3088,7 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
@@ -2815,16 +3096,16 @@
       <c r="I26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>184</v>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2836,7 +3117,7 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
@@ -2844,16 +3125,16 @@
       <c r="H27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>185</v>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2865,7 +3146,7 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
@@ -2873,19 +3154,19 @@
       <c r="I28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>186</v>
+      <c r="M28" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2905,16 +3186,16 @@
       <c r="I29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
-        <v>187</v>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2934,16 +3215,16 @@
       <c r="I30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>188</v>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2963,16 +3244,16 @@
       <c r="I31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" t="s">
-        <v>189</v>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2986,16 +3267,16 @@
       <c r="F32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" t="s">
-        <v>190</v>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -3015,16 +3296,16 @@
       <c r="J33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>191</v>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -3044,16 +3325,16 @@
       <c r="I34" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>192</v>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -3070,16 +3351,16 @@
       <c r="H35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>193</v>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -3099,16 +3380,16 @@
       <c r="I36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>194</v>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -3131,16 +3412,16 @@
       <c r="I37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>195</v>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -3160,16 +3441,16 @@
       <c r="I38" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
-        <v>196</v>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3189,16 +3470,16 @@
       <c r="H39" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>197</v>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3218,19 +3499,19 @@
       <c r="I40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" t="s">
-        <v>198</v>
+      <c r="M40" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3250,16 +3531,16 @@
       <c r="I41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" t="s">
-        <v>199</v>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3279,16 +3560,16 @@
       <c r="I42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" t="s">
-        <v>200</v>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3308,16 +3589,16 @@
       <c r="I43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" t="s">
-        <v>201</v>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3331,16 +3612,16 @@
       <c r="F44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" t="s">
-        <v>202</v>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3360,16 +3641,16 @@
       <c r="J45" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
-        <v>203</v>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3389,16 +3670,16 @@
       <c r="I46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" t="s">
-        <v>204</v>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3415,16 +3696,16 @@
       <c r="H47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" t="s">
-        <v>205</v>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3444,16 +3725,16 @@
       <c r="I48" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" t="s">
-        <v>206</v>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3476,16 +3757,16 @@
       <c r="I49" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" t="s">
-        <v>207</v>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3505,16 +3786,16 @@
       <c r="I50" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" t="s">
-        <v>208</v>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3534,16 +3815,16 @@
       <c r="H51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" t="s">
-        <v>209</v>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3563,19 +3844,19 @@
       <c r="I52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" t="s">
-        <v>210</v>
+      <c r="M52" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3587,21 +3868,15 @@
         <v>115</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>125</v>
-      </c>
-      <c r="B54" t="s">
-        <v>211</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3610,22 +3885,16 @@
         <v>114</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" t="s">
-        <v>117</v>
-      </c>
+      <c r="M54" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
         <v>36</v>
       </c>
@@ -3636,7 +3905,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
@@ -3645,12 +3914,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" t="s">
-        <v>212</v>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3664,19 +3933,13 @@
       <c r="F56" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="L56" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>125</v>
-      </c>
-      <c r="B57" t="s">
-        <v>213</v>
-      </c>
+      <c r="M56" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3690,17 +3953,11 @@
       <c r="G57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>35</v>
-      </c>
-      <c r="B58" t="s">
-        <v>118</v>
-      </c>
+      <c r="M57" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C58" s="1" t="s">
         <v>36</v>
       </c>
@@ -3720,12 +3977,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>125</v>
-      </c>
-      <c r="B59" t="s">
-        <v>214</v>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3739,19 +3996,13 @@
       <c r="F59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L59" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" t="s">
-        <v>215</v>
-      </c>
+      <c r="M59" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -3765,17 +4016,11 @@
       <c r="G60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L60" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>35</v>
-      </c>
-      <c r="B61" t="s">
-        <v>119</v>
-      </c>
+      <c r="M60" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C61" s="1" t="s">
         <v>36</v>
       </c>
@@ -3793,6 +4038,84 @@
       </c>
       <c r="I61" s="1" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3810,12 +4133,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="26.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="26.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3932,14 +4255,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3969,11 +4292,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>217</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3985,18 +4308,18 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>218</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4015,11 +4338,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>219</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4038,11 +4361,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>220</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4061,11 +4384,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>221</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4084,11 +4407,11 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>36</v>
@@ -4104,11 +4427,11 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>36</v>
@@ -4124,11 +4447,11 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>123</v>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>36</v>
@@ -4153,14 +4476,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4187,11 +4510,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>222</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4203,18 +4526,18 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>223</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4233,11 +4556,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>224</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4256,11 +4579,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>225</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4279,11 +4602,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>226</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4311,12 +4634,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4340,11 +4663,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>216</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4360,11 +4683,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>120</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>36</v>

--- a/KatalonData/RADTestData/BeforePayments.xlsx
+++ b/KatalonData/RADTestData/BeforePayments.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5865EEBB-5A1B-47FE-8F5F-EAC23505C708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E003C6B2-D428-4089-8298-A7532B1DF5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="11325" activeTab="5" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="228">
   <si>
     <t>Result</t>
   </si>
@@ -399,632 +399,343 @@
     <t>Mon Feb 17 19:38:28 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 17 19:43:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 17 19:44:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 17 19:44:59 EST 2025</t>
-  </si>
-  <si>
     <t>Incorrect App ID</t>
   </si>
   <si>
+    <t>This is in QA and Demo but not in Production</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>MFInsNum</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:23:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:24:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:24:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:25:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:25:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:26:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:27:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:27:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:28:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:29:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:30:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:30:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:31:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:32:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:32:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:33:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:34:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:35:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:35:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:36:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:37:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:38:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:38:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:39:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:40:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:41:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:41:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:42:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:43:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:43:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:44:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:45:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:46:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:46:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:47:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:47:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:48:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:49:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:49:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:50:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:51:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:51:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:52:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:53:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:53:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:54:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:54:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:55:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:56:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:56:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:57:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:58:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:58:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:59:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:00:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:00:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:01:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:02:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:02:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:03:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:04:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:04:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:05:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:05:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:06:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:07:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:07:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:08:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:09:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:10:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:10:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:11:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:11:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:12:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:13:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:13:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:14:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:15:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:15:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:16:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:17:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:17:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:18:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:19:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:19:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:20:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:21:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:21:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:22:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:23:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:23:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:24:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:25:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:26:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:26:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:27:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:28:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:29:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 03:30:02 EDT 2026</t>
+  </si>
+  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>This is in QA and Demo but not in Production</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:05:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:06:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:07:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:08:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:09:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:10:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:12:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:13:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:15:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:16:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:17:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:18:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:19:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:20:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:21:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:22:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:24:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:25:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:26:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:27:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:28:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:29:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:31:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:32:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:35:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:36:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:37:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:38:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:40:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:41:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:42:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:43:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:44:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:45:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:46:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:48:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:49:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:50:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:51:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:52:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:53:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:54:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:56:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:57:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:58:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 19:59:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:00:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:01:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:02:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:04:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:05:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:06:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:07:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:08:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:09:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:10:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:12:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:13:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:14:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:15:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:16:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:17:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:18:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:20:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:21:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:22:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:23:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:24:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:25:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:26:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:28:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:29:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:30:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:32:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:33:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:34:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:36:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:37:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:38:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:39:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:40:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:43:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:50:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:51:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:52:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:53:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:55:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:56:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:57:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:58:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 20:59:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:00:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:02:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 16:56:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>MFInsNum</t>
-  </si>
-  <si>
-    <t>Motor Fuel Floor Tax</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:27:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:27:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:28:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:29:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:30:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:23:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:24:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:24:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:25:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:25:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:26:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:27:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:27:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:28:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:29:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:30:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:30:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:31:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:32:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:32:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:33:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:34:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:35:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:35:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:36:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:37:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:38:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:38:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:39:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:40:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:41:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:41:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:42:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:43:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:43:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:44:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:45:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:46:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:46:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:47:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:47:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:48:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:49:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:49:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:50:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:51:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:51:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:52:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:53:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:53:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:54:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:54:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:55:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:56:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:56:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:57:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:58:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:58:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:59:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:00:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:00:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:01:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:02:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:02:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:03:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:04:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:04:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:05:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:05:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:06:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:07:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:07:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:08:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:09:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:10:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:10:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:11:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:11:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:12:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:13:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:13:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:14:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:15:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:15:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:16:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:17:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:17:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:18:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:19:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:19:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:20:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:21:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:21:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:22:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:23:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:23:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:24:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:25:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:26:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:26:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:27:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:28:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:29:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 03:30:02 EDT 2026</t>
+    <t>Sun Aug 02 14:12:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:14:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:14:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:21:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:22:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:23:14 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1397,17 +1108,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1447,7 +1158,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1459,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -1476,7 +1187,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1488,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -1505,7 +1216,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1517,7 +1228,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1537,7 +1248,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1549,7 +1260,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1569,7 +1280,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1581,7 +1292,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1601,7 +1312,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1613,7 +1324,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
@@ -1633,7 +1344,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1645,7 +1356,7 @@
         <v>115</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>102</v>
@@ -1666,16 +1377,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1715,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1738,7 +1449,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1761,7 +1472,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1784,7 +1495,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1810,7 +1521,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1836,7 +1547,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1859,7 +1570,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1882,7 +1593,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>239</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1905,7 +1616,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1928,7 +1639,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1951,7 +1662,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1974,7 +1685,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1997,7 +1708,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2020,7 +1731,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2040,7 +1751,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2066,7 +1777,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2089,7 +1800,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>248</v>
+        <v>145</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2129,7 +1840,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2141,7 +1852,7 @@
         <v>115</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
@@ -2158,7 +1869,7 @@
         <v>32</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2174,15 +1885,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2219,7 +1930,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>250</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2245,7 +1956,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2268,7 +1979,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2294,7 +2005,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2320,7 +2031,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2346,7 +2057,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2381,17 +2092,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
-    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
-    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
+    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2426,7 +2137,7 @@
         <v>112</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>47</v>
@@ -2440,7 +2151,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2463,7 +2174,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2489,7 +2200,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2515,7 +2226,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2541,7 +2252,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2567,7 +2278,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2590,7 +2301,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2616,7 +2327,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2642,7 +2353,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>264</v>
+        <v>161</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2668,7 +2379,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>265</v>
+        <v>162</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2694,7 +2405,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>266</v>
+        <v>163</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2717,7 +2428,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>267</v>
+        <v>164</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2743,7 +2454,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>268</v>
+        <v>165</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2769,7 +2480,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>269</v>
+        <v>166</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2795,7 +2506,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2821,7 +2532,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>271</v>
+        <v>168</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2833,7 +2544,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -2850,7 +2561,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>272</v>
+        <v>169</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2862,7 +2573,7 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
@@ -2879,7 +2590,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>273</v>
+        <v>170</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2891,7 +2602,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -2908,7 +2619,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2931,7 +2642,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2943,7 +2654,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>98</v>
@@ -2960,7 +2671,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>276</v>
+        <v>173</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2972,7 +2683,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
@@ -2989,7 +2700,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>277</v>
+        <v>174</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -3001,7 +2712,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>32</v>
@@ -3015,7 +2726,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>278</v>
+        <v>175</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -3027,7 +2738,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
@@ -3044,7 +2755,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>279</v>
+        <v>176</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -3056,7 +2767,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -3076,7 +2787,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>280</v>
+        <v>177</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -3088,7 +2799,7 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
@@ -3105,7 +2816,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -3117,7 +2828,7 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
@@ -3134,7 +2845,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>282</v>
+        <v>179</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -3146,7 +2857,7 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
@@ -3158,7 +2869,7 @@
         <v>92</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
@@ -3166,7 +2877,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>283</v>
+        <v>180</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -3195,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -3224,7 +2935,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -3253,7 +2964,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>286</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -3276,7 +2987,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>287</v>
+        <v>184</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -3305,7 +3016,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -3334,7 +3045,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>289</v>
+        <v>186</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -3360,7 +3071,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>290</v>
+        <v>187</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -3389,7 +3100,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>291</v>
+        <v>188</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -3421,7 +3132,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -3450,7 +3161,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>293</v>
+        <v>190</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3479,7 +3190,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>294</v>
+        <v>191</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3503,7 +3214,7 @@
         <v>92</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.45">
@@ -3511,7 +3222,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3540,7 +3251,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>296</v>
+        <v>193</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3569,7 +3280,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>297</v>
+        <v>194</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3598,7 +3309,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>298</v>
+        <v>195</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3621,7 +3332,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>299</v>
+        <v>196</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3650,7 +3361,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>300</v>
+        <v>197</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3679,7 +3390,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>301</v>
+        <v>198</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3705,7 +3416,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>302</v>
+        <v>199</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3734,7 +3445,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>303</v>
+        <v>200</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3766,7 +3477,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>304</v>
+        <v>201</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3795,7 +3506,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>305</v>
+        <v>202</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3824,7 +3535,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>306</v>
+        <v>203</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3848,7 +3559,7 @@
         <v>92</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.45">
@@ -3856,7 +3567,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>307</v>
+        <v>204</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3868,15 +3579,21 @@
         <v>115</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="C54" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3885,13 +3602,13 @@
         <v>114</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.45">
@@ -3905,7 +3622,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
@@ -3919,7 +3636,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>308</v>
+        <v>205</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3934,12 +3651,18 @@
         <v>113</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>223</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3954,7 +3677,7 @@
         <v>32</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.45">
@@ -3982,7 +3705,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>309</v>
+        <v>206</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3997,12 +3720,18 @@
         <v>37</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="C60" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -4017,7 +3746,7 @@
         <v>32</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.45">
@@ -4045,7 +3774,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>310</v>
+        <v>207</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -4054,10 +3783,10 @@
         <v>16</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>101</v>
@@ -4071,7 +3800,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>311</v>
+        <v>208</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -4080,7 +3809,7 @@
         <v>16</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>113</v>
@@ -4096,8 +3825,8 @@
       <c r="A64" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B64" t="s" s="1">
-        <v>312</v>
+      <c r="B64" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -4106,7 +3835,7 @@
         <v>16</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>37</v>
@@ -4133,12 +3862,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="26.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="26.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4255,14 +3984,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -4296,7 +4025,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>314</v>
+        <v>211</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4308,7 +4037,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>93</v>
@@ -4319,7 +4048,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>315</v>
+        <v>212</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4342,7 +4071,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>316</v>
+        <v>213</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4365,7 +4094,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>317</v>
+        <v>214</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4388,7 +4117,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4411,10 +4140,10 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>16</v>
@@ -4423,7 +4152,7 @@
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
@@ -4431,10 +4160,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>118</v>
+        <v>226</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -4443,7 +4172,7 @@
         <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
@@ -4451,10 +4180,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -4463,7 +4192,7 @@
         <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -4476,14 +4205,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4514,7 +4243,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>319</v>
+        <v>216</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4526,7 +4255,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>93</v>
@@ -4537,7 +4266,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>320</v>
+        <v>217</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4560,7 +4289,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>218</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4583,7 +4312,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>322</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4606,7 +4335,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>323</v>
+        <v>220</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4634,12 +4363,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4667,7 +4396,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>313</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
